--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Índice de envejecimiento</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="730">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -73,18 +73,18 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
+    <t xml:space="preserve">11402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Ibáñez</t>
+  </si>
+  <si>
     <t xml:space="preserve">12102</t>
   </si>
   <si>
     <t xml:space="preserve">Laguna Blanca</t>
   </si>
   <si>
-    <t xml:space="preserve">11402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Ibáñez</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -115,36 +115,36 @@
     <t xml:space="preserve">Porvenir</t>
   </si>
   <si>
+    <t xml:space="preserve">12402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torres del Paine</t>
+  </si>
+  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">12402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torres del Paine</t>
-  </si>
-  <si>
     <t xml:space="preserve">11101</t>
   </si>
   <si>
     <t xml:space="preserve">Coyhaique</t>
   </si>
   <si>
+    <t xml:space="preserve">11201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
     <t xml:space="preserve">12303</t>
   </si>
   <si>
     <t xml:space="preserve">Timaukel</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">12302</t>
   </si>
   <si>
@@ -181,6 +181,21 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">centro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrozona Centro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
@@ -190,21 +205,6 @@
     <t xml:space="preserve">Providencia</t>
   </si>
   <si>
-    <t xml:space="preserve">centro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macrozona Centro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nuble</t>
   </si>
   <si>
@@ -214,6 +214,12 @@
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
+    <t xml:space="preserve">16204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valparaiso</t>
   </si>
   <si>
@@ -232,12 +238,6 @@
     <t xml:space="preserve">Paredones</t>
   </si>
   <si>
-    <t xml:space="preserve">16204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
     <t xml:space="preserve">5605</t>
   </si>
   <si>
@@ -256,34 +256,40 @@
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
+    <t xml:space="preserve">5604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
     <t xml:space="preserve">6309</t>
   </si>
   <si>
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
-    <t xml:space="preserve">5604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
     <t xml:space="preserve">7309</t>
   </si>
   <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
+    <t xml:space="preserve">13132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
     <t xml:space="preserve">7107</t>
   </si>
   <si>
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
-    <t xml:space="preserve">13132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
+    <t xml:space="preserve">7302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
     <t xml:space="preserve">6202</t>
@@ -292,12 +298,6 @@
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
-    <t xml:space="preserve">7302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
     <t xml:space="preserve">6205</t>
   </si>
   <si>
@@ -328,18 +328,18 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
+    <t xml:space="preserve">16107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillón</t>
+  </si>
+  <si>
     <t xml:space="preserve">6304</t>
   </si>
   <si>
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">16107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillón</t>
-  </si>
-  <si>
     <t xml:space="preserve">7203</t>
   </si>
   <si>
@@ -352,6 +352,18 @@
     <t xml:space="preserve">Treguaco</t>
   </si>
   <si>
+    <t xml:space="preserve">7303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinto</t>
+  </si>
+  <si>
     <t xml:space="preserve">13118</t>
   </si>
   <si>
@@ -364,10 +376,10 @@
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
-    <t xml:space="preserve">16106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinto</t>
+    <t xml:space="preserve">5801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
     <t xml:space="preserve">7202</t>
@@ -376,22 +388,22 @@
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
-    <t xml:space="preserve">7303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
     <t xml:space="preserve">16203</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
-    <t xml:space="preserve">5801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
+    <t xml:space="preserve">16108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peralillo</t>
   </si>
   <si>
     <t xml:space="preserve">5405</t>
@@ -400,18 +412,6 @@
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
-    <t xml:space="preserve">16108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peralillo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6306</t>
   </si>
   <si>
@@ -424,16 +424,22 @@
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
+    <t xml:space="preserve">5101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">13129</t>
   </si>
   <si>
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
-    <t xml:space="preserve">5101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
+    <t xml:space="preserve">7201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">6103</t>
@@ -442,18 +448,18 @@
     <t xml:space="preserve">Coinco</t>
   </si>
   <si>
-    <t xml:space="preserve">7201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
     <t xml:space="preserve">16305</t>
   </si>
   <si>
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
+    <t xml:space="preserve">16104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
     <t xml:space="preserve">13110</t>
   </si>
   <si>
@@ -466,12 +472,6 @@
     <t xml:space="preserve">Papudo</t>
   </si>
   <si>
-    <t xml:space="preserve">16104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
     <t xml:space="preserve">5603</t>
   </si>
   <si>
@@ -484,106 +484,118 @@
     <t xml:space="preserve">San Carlos</t>
   </si>
   <si>
+    <t xml:space="preserve">5606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
     <t xml:space="preserve">6109</t>
   </si>
   <si>
     <t xml:space="preserve">Malloa</t>
   </si>
   <si>
-    <t xml:space="preserve">5404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6302</t>
   </si>
   <si>
     <t xml:space="preserve">Chépica</t>
   </si>
   <si>
+    <t xml:space="preserve">16109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yungay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litueche</t>
+  </si>
+  <si>
     <t xml:space="preserve">6113</t>
   </si>
   <si>
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
+    <t xml:space="preserve">7106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
     <t xml:space="preserve">7407</t>
   </si>
   <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
-    <t xml:space="preserve">6203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Litueche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yungay</t>
-  </si>
-  <si>
     <t xml:space="preserve">5105</t>
   </si>
   <si>
     <t xml:space="preserve">Puchuncaví</t>
   </si>
   <si>
+    <t xml:space="preserve">5506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulnes</t>
+  </si>
+  <si>
     <t xml:space="preserve">13117</t>
   </si>
   <si>
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
-    <t xml:space="preserve">5506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
     <t xml:space="preserve">13109</t>
   </si>
   <si>
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
+    <t xml:space="preserve">16105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">13104</t>
   </si>
   <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
-    <t xml:space="preserve">16102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulnes</t>
+    <t xml:space="preserve">6117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
   </si>
   <si>
     <t xml:space="preserve">13111</t>
@@ -598,16 +610,46 @@
     <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
-    <t xml:space="preserve">6117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
+    <t xml:space="preserve">7305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
   </si>
   <si>
     <t xml:space="preserve">16304</t>
@@ -616,52 +658,16 @@
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">5705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
     <t xml:space="preserve">6112</t>
   </si>
   <si>
     <t xml:space="preserve">Peumo</t>
   </si>
   <si>
-    <t xml:space="preserve">13131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
+    <t xml:space="preserve">7405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retiro</t>
   </si>
   <si>
     <t xml:space="preserve">7404</t>
@@ -670,12 +676,6 @@
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
-    <t xml:space="preserve">7405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
     <t xml:space="preserve">6308</t>
   </si>
   <si>
@@ -694,22 +694,40 @@
     <t xml:space="preserve">San José de Maipo</t>
   </si>
   <si>
+    <t xml:space="preserve">5804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
     <t xml:space="preserve">6201</t>
   </si>
   <si>
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
-    <t xml:space="preserve">5804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alemana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
+    <t xml:space="preserve">6310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
   </si>
   <si>
     <t xml:space="preserve">6104</t>
@@ -724,22 +742,10 @@
     <t xml:space="preserve">Teno</t>
   </si>
   <si>
-    <t xml:space="preserve">6310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codegua</t>
+    <t xml:space="preserve">5402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
   </si>
   <si>
     <t xml:space="preserve">7110</t>
@@ -748,10 +754,10 @@
     <t xml:space="preserve">San Rafael</t>
   </si>
   <si>
-    <t xml:space="preserve">5402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
+    <t xml:space="preserve">5601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
     <t xml:space="preserve">13116</t>
@@ -760,10 +766,10 @@
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
-    <t xml:space="preserve">5601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
+    <t xml:space="preserve">7401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
   </si>
   <si>
     <t xml:space="preserve">13126</t>
@@ -772,28 +778,34 @@
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">7401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
     <t xml:space="preserve">5802</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
+    <t xml:space="preserve">16101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chillán</t>
+  </si>
+  <si>
     <t xml:space="preserve">6305</t>
   </si>
   <si>
     <t xml:space="preserve">Nancagua</t>
   </si>
   <si>
-    <t xml:space="preserve">16101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chillán</t>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
   </si>
   <si>
     <t xml:space="preserve">13127</t>
@@ -802,16 +814,22 @@
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
-    <t xml:space="preserve">5702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
+    <t xml:space="preserve">13105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
     <t xml:space="preserve">5704</t>
@@ -820,22 +838,16 @@
     <t xml:space="preserve">Panquehue</t>
   </si>
   <si>
-    <t xml:space="preserve">5102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Bosque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Cabras</t>
+    <t xml:space="preserve">7104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
   </si>
   <si>
     <t xml:space="preserve">6303</t>
@@ -844,40 +856,34 @@
     <t xml:space="preserve">Chimbarongo</t>
   </si>
   <si>
-    <t xml:space="preserve">5706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
     <t xml:space="preserve">7101</t>
   </si>
   <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
+    <t xml:space="preserve">13202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
     <t xml:space="preserve">13505</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro</t>
   </si>
   <si>
-    <t xml:space="preserve">13202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empedrado</t>
+    <t xml:space="preserve">5503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
     <t xml:space="preserve">7306</t>
@@ -886,10 +892,34 @@
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
-    <t xml:space="preserve">5503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
+    <t xml:space="preserve">7408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colbún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Javier</t>
   </si>
   <si>
     <t xml:space="preserve">13130</t>
@@ -898,40 +928,28 @@
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
-    <t xml:space="preserve">7408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colbún</t>
-  </si>
-  <si>
     <t xml:space="preserve">13103</t>
   </si>
   <si>
     <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
-    <t xml:space="preserve">6105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doñihue</t>
+    <t xml:space="preserve">6111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
     <t xml:space="preserve">13101</t>
@@ -940,22 +958,22 @@
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">5304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivar</t>
+    <t xml:space="preserve">6301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coihueco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
     <t xml:space="preserve">13504</t>
@@ -964,10 +982,16 @@
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">6301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fernando</t>
+    <t xml:space="preserve">6101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
     <t xml:space="preserve">16206</t>
@@ -976,30 +1000,6 @@
     <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
-    <t xml:space="preserve">13122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rancagua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coihueco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">5701</t>
   </si>
   <si>
@@ -1012,30 +1012,30 @@
     <t xml:space="preserve">Mostazal</t>
   </si>
   <si>
+    <t xml:space="preserve">7301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">13106</t>
   </si>
   <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">7301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rengo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">7102</t>
   </si>
   <si>
@@ -1048,24 +1048,24 @@
     <t xml:space="preserve">Talagante</t>
   </si>
   <si>
+    <t xml:space="preserve">13603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requínoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">13108</t>
   </si>
   <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
-    <t xml:space="preserve">6116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requínoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
     <t xml:space="preserve">13201</t>
   </si>
   <si>
@@ -1090,18 +1090,18 @@
     <t xml:space="preserve">La Cruz</t>
   </si>
   <si>
+    <t xml:space="preserve">16103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chillán Viejo</t>
+  </si>
+  <si>
     <t xml:space="preserve">5303</t>
   </si>
   <si>
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
-    <t xml:space="preserve">16103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chillán Viejo</t>
-  </si>
-  <si>
     <t xml:space="preserve">13128</t>
   </si>
   <si>
@@ -1132,18 +1132,18 @@
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
+    <t xml:space="preserve">13115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
     <t xml:space="preserve">5502</t>
   </si>
   <si>
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
-    <t xml:space="preserve">13115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
     <t xml:space="preserve">13112</t>
   </si>
   <si>
@@ -1180,18 +1180,18 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
+    <t xml:space="preserve">13402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
     <t xml:space="preserve">13604</t>
   </si>
   <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">13402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
     <t xml:space="preserve">13125</t>
   </si>
   <si>
@@ -1282,18 +1282,18 @@
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
+    <t xml:space="preserve">4103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andacollo</t>
+  </si>
+  <si>
     <t xml:space="preserve">4106</t>
   </si>
   <si>
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
-    <t xml:space="preserve">4103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andacollo</t>
-  </si>
-  <si>
     <t xml:space="preserve">4203</t>
   </si>
   <si>
@@ -1336,16 +1336,22 @@
     <t xml:space="preserve">Vallenar</t>
   </si>
   <si>
+    <t xml:space="preserve">3303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina</t>
+  </si>
+  <si>
     <t xml:space="preserve">15202</t>
   </si>
   <si>
     <t xml:space="preserve">General Lagos</t>
   </si>
   <si>
-    <t xml:space="preserve">3303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freirina</t>
+    <t xml:space="preserve">3201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
     <t xml:space="preserve">3102</t>
@@ -1354,12 +1360,6 @@
     <t xml:space="preserve">Caldera</t>
   </si>
   <si>
-    <t xml:space="preserve">3201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">4101</t>
   </si>
   <si>
@@ -1393,24 +1393,24 @@
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
+    <t xml:space="preserve">1402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica</t>
+  </si>
+  <si>
     <t xml:space="preserve">4104</t>
   </si>
   <si>
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">1402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">1405</t>
   </si>
   <si>
@@ -1522,6 +1522,12 @@
     <t xml:space="preserve">Biobio</t>
   </si>
   <si>
+    <t xml:space="preserve">8310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
     <t xml:space="preserve">8308</t>
   </si>
   <si>
@@ -1534,10 +1540,10 @@
     <t xml:space="preserve">Maullín</t>
   </si>
   <si>
-    <t xml:space="preserve">8310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
+    <t xml:space="preserve">8313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
     <t xml:space="preserve">8104</t>
@@ -1552,12 +1558,6 @@
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
-    <t xml:space="preserve">8313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yumbel</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Araucania</t>
   </si>
   <si>
@@ -1567,36 +1567,36 @@
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
+    <t xml:space="preserve">8302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">8309</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
+    <t xml:space="preserve">10210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
     <t xml:space="preserve">10206</t>
   </si>
   <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
-    <t xml:space="preserve">8302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
     <t xml:space="preserve">10104</t>
   </si>
   <si>
@@ -1609,36 +1609,36 @@
     <t xml:space="preserve">Curacautín</t>
   </si>
   <si>
+    <t xml:space="preserve">10305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
     <t xml:space="preserve">8101</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">10305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Negro</t>
-  </si>
-  <si>
     <t xml:space="preserve">8110</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
+    <t xml:space="preserve">10303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
     <t xml:space="preserve">9103</t>
   </si>
   <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
-    <t xml:space="preserve">10303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
     <t xml:space="preserve">8111</t>
   </si>
   <si>
@@ -1657,24 +1657,30 @@
     <t xml:space="preserve">Teodoro Schmidt</t>
   </si>
   <si>
+    <t xml:space="preserve">9118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
     <t xml:space="preserve">10304</t>
   </si>
   <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
-    <t xml:space="preserve">9118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
     <t xml:space="preserve">9105</t>
   </si>
   <si>
     <t xml:space="preserve">Freire</t>
   </si>
   <si>
+    <t xml:space="preserve">10204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
     <t xml:space="preserve">9110</t>
   </si>
   <si>
@@ -1693,36 +1699,36 @@
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
+    <t xml:space="preserve">10106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
     <t xml:space="preserve">9210</t>
   </si>
   <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
-    <t xml:space="preserve">10106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Muermos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Rios</t>
   </si>
   <si>
@@ -1732,10 +1738,10 @@
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
-    <t xml:space="preserve">10204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
+    <t xml:space="preserve">9109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loncoche</t>
   </si>
   <si>
     <t xml:space="preserve">10401</t>
@@ -1744,28 +1750,34 @@
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">9109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loncoche</t>
-  </si>
-  <si>
     <t xml:space="preserve">14201</t>
   </si>
   <si>
     <t xml:space="preserve">La Unión</t>
   </si>
   <si>
+    <t xml:space="preserve">10207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
     <t xml:space="preserve">9206</t>
   </si>
   <si>
     <t xml:space="preserve">Los Sauces</t>
   </si>
   <si>
-    <t xml:space="preserve">10207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queilén</t>
+    <t xml:space="preserve">9114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitrufquén</t>
   </si>
   <si>
     <t xml:space="preserve">8109</t>
@@ -1774,24 +1786,18 @@
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
-    <t xml:space="preserve">8103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">14203</t>
   </si>
   <si>
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
+    <t xml:space="preserve">9116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saavedra</t>
+  </si>
+  <si>
     <t xml:space="preserve">9211</t>
   </si>
   <si>
@@ -1816,10 +1822,28 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
-    <t xml:space="preserve">9116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saavedra</t>
+    <t xml:space="preserve">10302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
     <t xml:space="preserve">8107</t>
@@ -1828,28 +1852,10 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">10302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Octay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumaco</t>
+    <t xml:space="preserve">9111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Imperial</t>
   </si>
   <si>
     <t xml:space="preserve">14101</t>
@@ -1858,12 +1864,6 @@
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
-    <t xml:space="preserve">9111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Imperial</t>
-  </si>
-  <si>
     <t xml:space="preserve">14105</t>
   </si>
   <si>
@@ -1894,6 +1894,12 @@
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
+    <t xml:space="preserve">8303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
     <t xml:space="preserve">9201</t>
   </si>
   <si>
@@ -1903,10 +1909,10 @@
     <t xml:space="preserve">14104</t>
   </si>
   <si>
-    <t xml:space="preserve">8303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
+    <t xml:space="preserve">10102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
   </si>
   <si>
     <t xml:space="preserve">8307</t>
@@ -1915,10 +1921,10 @@
     <t xml:space="preserve">Negrete</t>
   </si>
   <si>
-    <t xml:space="preserve">10102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calbuco</t>
+    <t xml:space="preserve">8306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
     <t xml:space="preserve">8205</t>
@@ -1927,12 +1933,6 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">8306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
     <t xml:space="preserve">9106</t>
   </si>
   <si>
@@ -1957,6 +1957,12 @@
     <t xml:space="preserve">Panguipulli</t>
   </si>
   <si>
+    <t xml:space="preserve">9202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collipulli</t>
+  </si>
+  <si>
     <t xml:space="preserve">9209</t>
   </si>
   <si>
@@ -1969,12 +1975,6 @@
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
-    <t xml:space="preserve">9202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">10403</t>
   </si>
   <si>
@@ -2005,36 +2005,36 @@
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
+    <t xml:space="preserve">14202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
     <t xml:space="preserve">9205</t>
   </si>
   <si>
     <t xml:space="preserve">Lonquimay</t>
   </si>
   <si>
-    <t xml:space="preserve">14202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futaleufú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Castro</t>
-  </si>
-  <si>
     <t xml:space="preserve">9119</t>
   </si>
   <si>
@@ -2065,16 +2065,22 @@
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
+    <t xml:space="preserve">10205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">9121</t>
   </si>
   <si>
     <t xml:space="preserve">Cholchol</t>
   </si>
   <si>
-    <t xml:space="preserve">10205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalcahue</t>
+    <t xml:space="preserve">14106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
     <t xml:space="preserve">8102</t>
@@ -2083,30 +2089,24 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">14106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
     <t xml:space="preserve">9115</t>
   </si>
   <si>
     <t xml:space="preserve">Pucón</t>
   </si>
   <si>
+    <t xml:space="preserve">9112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
     <t xml:space="preserve">10109</t>
   </si>
   <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
-    <t xml:space="preserve">9112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
     <t xml:space="preserve">8206</t>
   </si>
   <si>
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:00</t>
+    <t xml:space="preserve">2026-09-04 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2173,16 +2173,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_d_enveje_a_2022.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Indice de envejecimiento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -2664,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>167.74</v>
+        <v>182.46</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
@@ -2675,10 +2684,10 @@
         <v>2022</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
@@ -2696,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>154.29</v>
+        <v>162.5</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>8</v>
@@ -2707,10 +2716,10 @@
         <v>2022</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -2728,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>153.09</v>
+        <v>158.82</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>8</v>
@@ -2760,7 +2769,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>130.92</v>
+        <v>141.71</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>8</v>
@@ -2792,7 +2801,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>117.75</v>
+        <v>126.81</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>8</v>
@@ -2824,7 +2833,7 @@
         <v>8</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>112.09</v>
+        <v>120.76</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>8</v>
@@ -2856,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>8</v>
@@ -2888,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>94.54</v>
+        <v>100.88</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>8</v>
@@ -2899,10 +2908,10 @@
         <v>2022</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>32</v>
@@ -2920,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>91.71</v>
+        <v>100</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>8</v>
@@ -2931,10 +2940,10 @@
         <v>2022</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>34</v>
@@ -2952,7 +2961,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>90.32</v>
+        <v>97.24</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>8</v>
@@ -2984,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>83.11</v>
+        <v>89.66</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>8</v>
@@ -2995,10 +3004,10 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>38</v>
@@ -3016,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>82.76</v>
+        <v>89.38</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>8</v>
@@ -3027,10 +3036,10 @@
         <v>2022</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>40</v>
@@ -3048,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>82.33</v>
+        <v>88.89</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>8</v>
@@ -3080,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>82.22</v>
+        <v>86.72</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>8</v>
@@ -3112,7 +3121,7 @@
         <v>8</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>78.65</v>
+        <v>84.25</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>8</v>
@@ -3144,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>65.86</v>
+        <v>71.01</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>8</v>
@@ -3176,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>49.62</v>
+        <v>53.72</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>8</v>
@@ -3208,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>40</v>
+        <v>41.46</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>8</v>
@@ -3240,7 +3249,7 @@
         <v>8</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>36.24</v>
+        <v>38.12</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>8</v>
@@ -3251,7 +3260,7 @@
         <v>2022</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>54</v>
@@ -3272,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>200.09</v>
+        <v>216.12</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>8</v>
@@ -3283,7 +3292,7 @@
         <v>2022</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>59</v>
@@ -3304,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>199.45</v>
+        <v>213.08</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>8</v>
@@ -3336,7 +3345,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>194.76</v>
+        <v>210.71</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>8</v>
@@ -3347,17 +3356,17 @@
         <v>2022</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>57</v>
       </c>
@@ -3368,7 +3377,7 @@
         <v>8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>180.02</v>
+        <v>194.79</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>8</v>
@@ -3379,17 +3388,17 @@
         <v>2022</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F26" s="2" t="s">
         <v>57</v>
       </c>
@@ -3400,7 +3409,7 @@
         <v>8</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>178.77</v>
+        <v>192.67</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>8</v>
@@ -3411,10 +3420,10 @@
         <v>2022</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3432,7 +3441,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>177.95</v>
+        <v>192.32</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>8</v>
@@ -3446,7 +3455,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3464,7 +3473,7 @@
         <v>8</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>177.74</v>
+        <v>190.49</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>8</v>
@@ -3478,7 +3487,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3496,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>174.33</v>
+        <v>188.35</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>8</v>
@@ -3528,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>171.68</v>
+        <v>187.08</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>8</v>
@@ -3539,10 +3548,10 @@
         <v>2022</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3560,7 +3569,7 @@
         <v>8</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>170.33</v>
+        <v>181.95</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>8</v>
@@ -3571,10 +3580,10 @@
         <v>2022</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3592,7 +3601,7 @@
         <v>8</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>169.61</v>
+        <v>179.82</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>8</v>
@@ -3606,7 +3615,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3624,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>162.96</v>
+        <v>174.86</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>8</v>
@@ -3635,7 +3644,7 @@
         <v>2022</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>59</v>
@@ -3656,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>158.59</v>
+        <v>171.81</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>8</v>
@@ -3667,7 +3676,7 @@
         <v>2022</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>54</v>
@@ -3688,7 +3697,7 @@
         <v>8</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>158.48</v>
+        <v>171.4</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>8</v>
@@ -3699,10 +3708,10 @@
         <v>2022</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3720,7 +3729,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>157.8</v>
+        <v>170.35</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>8</v>
@@ -3731,10 +3740,10 @@
         <v>2022</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3752,7 +3761,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>157.18</v>
+        <v>169.41</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>8</v>
@@ -3766,7 +3775,7 @@
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3784,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>156.56</v>
+        <v>169</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>8</v>
@@ -3798,7 +3807,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3816,7 +3825,7 @@
         <v>8</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>155.45</v>
+        <v>165.58</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>8</v>
@@ -3830,7 +3839,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>97</v>
@@ -3848,7 +3857,7 @@
         <v>8</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>148.76</v>
+        <v>159.51</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>8</v>
@@ -3862,7 +3871,7 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>99</v>
@@ -3880,7 +3889,7 @@
         <v>8</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>147.35</v>
+        <v>158.37</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>8</v>
@@ -3912,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>146.99</v>
+        <v>157.73</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>8</v>
@@ -3923,10 +3932,10 @@
         <v>2022</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3944,7 +3953,7 @@
         <v>8</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>146.27</v>
+        <v>156.84</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>8</v>
@@ -3955,10 +3964,10 @@
         <v>2022</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3976,7 +3985,7 @@
         <v>8</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>145.86</v>
+        <v>156.29</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>8</v>
@@ -3990,7 +3999,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -4008,7 +4017,7 @@
         <v>8</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>143.53</v>
+        <v>153.6</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>8</v>
@@ -4040,7 +4049,7 @@
         <v>8</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>142.86</v>
+        <v>153.59</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>8</v>
@@ -4051,7 +4060,7 @@
         <v>2022</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>54</v>
@@ -4072,7 +4081,7 @@
         <v>8</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>142.06</v>
+        <v>153.03</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>8</v>
@@ -4083,10 +4092,10 @@
         <v>2022</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>113</v>
@@ -4104,7 +4113,7 @@
         <v>8</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>142.02</v>
+        <v>152.74</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>8</v>
@@ -4115,10 +4124,10 @@
         <v>2022</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4136,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>141.54</v>
+        <v>152.44</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>8</v>
@@ -4147,7 +4156,7 @@
         <v>2022</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>59</v>
@@ -4168,7 +4177,7 @@
         <v>8</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>141.16</v>
+        <v>151.42</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>8</v>
@@ -4179,10 +4188,10 @@
         <v>2022</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4200,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>140.49</v>
+        <v>151.13</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>8</v>
@@ -4211,10 +4220,10 @@
         <v>2022</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4232,7 +4241,7 @@
         <v>8</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>140.35</v>
+        <v>150.95</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>8</v>
@@ -4243,10 +4252,10 @@
         <v>2022</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4264,7 +4273,7 @@
         <v>8</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>140.27</v>
+        <v>150.61</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>8</v>
@@ -4275,10 +4284,10 @@
         <v>2022</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4296,7 +4305,7 @@
         <v>8</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>138.14</v>
+        <v>148.13</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>8</v>
@@ -4307,10 +4316,10 @@
         <v>2022</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4328,7 +4337,7 @@
         <v>8</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>136.85</v>
+        <v>147.16</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>8</v>
@@ -4339,10 +4348,10 @@
         <v>2022</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4360,7 +4369,7 @@
         <v>8</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>135.54</v>
+        <v>146.11</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>8</v>
@@ -4374,7 +4383,7 @@
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4392,7 +4401,7 @@
         <v>8</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>135.44</v>
+        <v>145.71</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>8</v>
@@ -4406,7 +4415,7 @@
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4424,7 +4433,7 @@
         <v>8</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>135.19</v>
+        <v>144.52</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>8</v>
@@ -4435,10 +4444,10 @@
         <v>2022</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4456,7 +4465,7 @@
         <v>8</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>134.26</v>
+        <v>143.71</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>8</v>
@@ -4467,10 +4476,10 @@
         <v>2022</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4488,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>134.01</v>
+        <v>143.03</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>8</v>
@@ -4499,10 +4508,10 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>139</v>
@@ -4520,7 +4529,7 @@
         <v>8</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>130.56</v>
+        <v>140.23</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>8</v>
@@ -4531,10 +4540,10 @@
         <v>2022</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>141</v>
@@ -4552,7 +4561,7 @@
         <v>8</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>130.55</v>
+        <v>139.92</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>8</v>
@@ -4584,7 +4593,7 @@
         <v>8</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>130.25</v>
+        <v>139.84</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>8</v>
@@ -4595,10 +4604,10 @@
         <v>2022</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4616,7 +4625,7 @@
         <v>8</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>129.6</v>
+        <v>139.75</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>8</v>
@@ -4627,10 +4636,10 @@
         <v>2022</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4648,7 +4657,7 @@
         <v>8</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>129.5</v>
+        <v>139.3</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>8</v>
@@ -4659,10 +4668,10 @@
         <v>2022</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>149</v>
@@ -4680,7 +4689,7 @@
         <v>8</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>129.19</v>
+        <v>138.69</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>8</v>
@@ -4694,7 +4703,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>151</v>
@@ -4712,7 +4721,7 @@
         <v>8</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>128.88</v>
+        <v>138.12</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>8</v>
@@ -4744,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>127.97</v>
+        <v>138.08</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>8</v>
@@ -4755,10 +4764,10 @@
         <v>2022</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4776,7 +4785,7 @@
         <v>8</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>127.61</v>
+        <v>137.37</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>8</v>
@@ -4790,7 +4799,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4808,7 +4817,7 @@
         <v>8</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>127.08</v>
+        <v>137.24</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>8</v>
@@ -4819,10 +4828,10 @@
         <v>2022</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>159</v>
@@ -4840,7 +4849,7 @@
         <v>8</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>126.96</v>
+        <v>136.6</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>8</v>
@@ -4854,7 +4863,7 @@
         <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4872,7 +4881,7 @@
         <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>126</v>
+        <v>135.61</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>8</v>
@@ -4883,10 +4892,10 @@
         <v>2022</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4904,7 +4913,7 @@
         <v>8</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>125.34</v>
+        <v>135.36</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>8</v>
@@ -4915,10 +4924,10 @@
         <v>2022</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4936,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>125.26</v>
+        <v>134.7</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>8</v>
@@ -4950,7 +4959,7 @@
         <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4968,7 +4977,7 @@
         <v>8</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>125.18</v>
+        <v>134.43</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>8</v>
@@ -4982,7 +4991,7 @@
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -5000,7 +5009,7 @@
         <v>8</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>124.65</v>
+        <v>134.22</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>8</v>
@@ -5011,10 +5020,10 @@
         <v>2022</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -5032,7 +5041,7 @@
         <v>8</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>124.57</v>
+        <v>134</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>8</v>
@@ -5046,7 +5055,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -5064,7 +5073,7 @@
         <v>8</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>123.13</v>
+        <v>132.73</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>8</v>
@@ -5075,10 +5084,10 @@
         <v>2022</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5096,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>123.07</v>
+        <v>132.67</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>8</v>
@@ -5110,7 +5119,7 @@
         <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>177</v>
@@ -5128,7 +5137,7 @@
         <v>8</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>123.06</v>
+        <v>132.48</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>8</v>
@@ -5142,7 +5151,7 @@
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5160,7 +5169,7 @@
         <v>8</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>122.41</v>
+        <v>132.38</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>8</v>
@@ -5171,10 +5180,10 @@
         <v>2022</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5192,7 +5201,7 @@
         <v>8</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>122.31</v>
+        <v>131.88</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>8</v>
@@ -5206,7 +5215,7 @@
         <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5224,7 +5233,7 @@
         <v>8</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>122.24</v>
+        <v>131.8</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>8</v>
@@ -5238,7 +5247,7 @@
         <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5256,7 +5265,7 @@
         <v>8</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>122.22</v>
+        <v>131.05</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>8</v>
@@ -5288,7 +5297,7 @@
         <v>8</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>122.08</v>
+        <v>131.03</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>8</v>
@@ -5302,7 +5311,7 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5320,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>121.97</v>
+        <v>130.99</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>8</v>
@@ -5334,7 +5343,7 @@
         <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>191</v>
@@ -5352,7 +5361,7 @@
         <v>8</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>121.72</v>
+        <v>130.73</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>8</v>
@@ -5363,10 +5372,10 @@
         <v>2022</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5384,7 +5393,7 @@
         <v>8</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>121.37</v>
+        <v>130.62</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>8</v>
@@ -5395,10 +5404,10 @@
         <v>2022</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5416,7 +5425,7 @@
         <v>8</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>121.16</v>
+        <v>130.25</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>8</v>
@@ -5427,10 +5436,10 @@
         <v>2022</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5448,7 +5457,7 @@
         <v>8</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>120.78</v>
+        <v>129.33</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>8</v>
@@ -5462,7 +5471,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>199</v>
@@ -5480,7 +5489,7 @@
         <v>8</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>120.74</v>
+        <v>129.13</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>8</v>
@@ -5494,7 +5503,7 @@
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5512,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>120.54</v>
+        <v>128.48</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>8</v>
@@ -5523,10 +5532,10 @@
         <v>2022</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>203</v>
@@ -5544,7 +5553,7 @@
         <v>8</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>120.37</v>
+        <v>128.34</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>8</v>
@@ -5558,7 +5567,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>205</v>
@@ -5576,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>119.89</v>
+        <v>128.14</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>8</v>
@@ -5587,10 +5596,10 @@
         <v>2022</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5608,7 +5617,7 @@
         <v>8</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>119.68</v>
+        <v>128.13</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>8</v>
@@ -5622,7 +5631,7 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>209</v>
@@ -5640,7 +5649,7 @@
         <v>8</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>119.58</v>
+        <v>127.75</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>8</v>
@@ -5651,10 +5660,10 @@
         <v>2022</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>211</v>
@@ -5672,7 +5681,7 @@
         <v>8</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>119.18</v>
+        <v>127.59</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>8</v>
@@ -5683,10 +5692,10 @@
         <v>2022</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>213</v>
@@ -5704,7 +5713,7 @@
         <v>8</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>118.7</v>
+        <v>127.5</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>8</v>
@@ -5718,7 +5727,7 @@
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5736,7 +5745,7 @@
         <v>8</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>118.45</v>
+        <v>127.02</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>8</v>
@@ -5750,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5768,7 +5777,7 @@
         <v>8</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>118.29</v>
+        <v>126.57</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>8</v>
@@ -5782,7 +5791,7 @@
         <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>219</v>
@@ -5800,7 +5809,7 @@
         <v>8</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>118.15</v>
+        <v>125.93</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>8</v>
@@ -5814,7 +5823,7 @@
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5832,7 +5841,7 @@
         <v>8</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>116.31</v>
+        <v>125.89</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>8</v>
@@ -5846,7 +5855,7 @@
         <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>223</v>
@@ -5864,7 +5873,7 @@
         <v>8</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>116.12</v>
+        <v>125.26</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>8</v>
@@ -5875,10 +5884,10 @@
         <v>2022</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>225</v>
@@ -5896,7 +5905,7 @@
         <v>8</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>115.74</v>
+        <v>124.11</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>8</v>
@@ -5910,7 +5919,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5928,7 +5937,7 @@
         <v>8</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>115.38</v>
+        <v>123.73</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>8</v>
@@ -5939,10 +5948,10 @@
         <v>2022</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5960,7 +5969,7 @@
         <v>8</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>115.06</v>
+        <v>123.32</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>8</v>
@@ -5974,7 +5983,7 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>231</v>
@@ -5992,7 +6001,7 @@
         <v>8</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>114.29</v>
+        <v>123.21</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>8</v>
@@ -6003,10 +6012,10 @@
         <v>2022</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>233</v>
@@ -6024,7 +6033,7 @@
         <v>8</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>114.23</v>
+        <v>122.96</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>8</v>
@@ -6035,10 +6044,10 @@
         <v>2022</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -6056,7 +6065,7 @@
         <v>8</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>114.14</v>
+        <v>122.75</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>8</v>
@@ -6067,10 +6076,10 @@
         <v>2022</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -6088,7 +6097,7 @@
         <v>8</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>113.93</v>
+        <v>122.64</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>8</v>
@@ -6099,10 +6108,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6120,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>113.93</v>
+        <v>122.6</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>8</v>
@@ -6131,10 +6140,10 @@
         <v>2022</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6152,7 +6161,7 @@
         <v>8</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>113.86</v>
+        <v>122.46</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>8</v>
@@ -6163,10 +6172,10 @@
         <v>2022</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>243</v>
@@ -6184,7 +6193,7 @@
         <v>8</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>113.35</v>
+        <v>122.12</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>8</v>
@@ -6195,10 +6204,10 @@
         <v>2022</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>245</v>
@@ -6216,7 +6225,7 @@
         <v>8</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>112.84</v>
+        <v>120.71</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>8</v>
@@ -6227,10 +6236,10 @@
         <v>2022</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>247</v>
@@ -6248,7 +6257,7 @@
         <v>8</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>112.27</v>
+        <v>120.29</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>8</v>
@@ -6259,7 +6268,7 @@
         <v>2022</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>54</v>
@@ -6280,7 +6289,7 @@
         <v>8</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>111.89</v>
+        <v>120.06</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>8</v>
@@ -6291,7 +6300,7 @@
         <v>2022</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>59</v>
@@ -6312,7 +6321,7 @@
         <v>8</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>111.67</v>
+        <v>119.11</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>8</v>
@@ -6326,7 +6335,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>253</v>
@@ -6344,7 +6353,7 @@
         <v>8</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>111.47</v>
+        <v>119.04</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>8</v>
@@ -6355,10 +6364,10 @@
         <v>2022</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6376,7 +6385,7 @@
         <v>8</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>110.77</v>
+        <v>119</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>8</v>
@@ -6387,10 +6396,10 @@
         <v>2022</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6408,7 +6417,7 @@
         <v>8</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>110.55</v>
+        <v>118.6</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>8</v>
@@ -6419,10 +6428,10 @@
         <v>2022</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>259</v>
@@ -6440,7 +6449,7 @@
         <v>8</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>109.84</v>
+        <v>117.6</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>8</v>
@@ -6454,7 +6463,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6472,7 +6481,7 @@
         <v>8</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>109.63</v>
+        <v>117.57</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>8</v>
@@ -6483,10 +6492,10 @@
         <v>2022</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6504,7 +6513,7 @@
         <v>8</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>109.47</v>
+        <v>117.27</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>8</v>
@@ -6515,10 +6524,10 @@
         <v>2022</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6536,7 +6545,7 @@
         <v>8</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>109.28</v>
+        <v>117.13</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>8</v>
@@ -6547,10 +6556,10 @@
         <v>2022</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6568,7 +6577,7 @@
         <v>8</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>109.26</v>
+        <v>117.04</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>8</v>
@@ -6579,10 +6588,10 @@
         <v>2022</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>269</v>
@@ -6600,7 +6609,7 @@
         <v>8</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>109.04</v>
+        <v>116.93</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>8</v>
@@ -6611,10 +6620,10 @@
         <v>2022</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>271</v>
@@ -6632,7 +6641,7 @@
         <v>8</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>108.9</v>
+        <v>116.69</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>8</v>
@@ -6643,10 +6652,10 @@
         <v>2022</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6664,7 +6673,7 @@
         <v>8</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>107.34</v>
+        <v>115.94</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>8</v>
@@ -6678,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>275</v>
@@ -6696,7 +6705,7 @@
         <v>8</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>107.31</v>
+        <v>115.66</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>8</v>
@@ -6707,10 +6716,10 @@
         <v>2022</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6728,7 +6737,7 @@
         <v>8</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>107.05</v>
+        <v>115.22</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>8</v>
@@ -6739,7 +6748,7 @@
         <v>2022</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>54</v>
@@ -6760,7 +6769,7 @@
         <v>8</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>106.66</v>
+        <v>114.71</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>8</v>
@@ -6774,7 +6783,7 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6792,7 +6801,7 @@
         <v>8</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>106.56</v>
+        <v>114.48</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>8</v>
@@ -6806,7 +6815,7 @@
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6824,7 +6833,7 @@
         <v>8</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>105.91</v>
+        <v>113.96</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>8</v>
@@ -6835,7 +6844,7 @@
         <v>2022</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>59</v>
@@ -6856,7 +6865,7 @@
         <v>8</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>105.9</v>
+        <v>113.84</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>8</v>
@@ -6867,10 +6876,10 @@
         <v>2022</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6888,7 +6897,7 @@
         <v>8</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>105.71</v>
+        <v>113.73</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>8</v>
@@ -6899,10 +6908,10 @@
         <v>2022</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6920,7 +6929,7 @@
         <v>8</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>105.55</v>
+        <v>113.39</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>8</v>
@@ -6931,7 +6940,7 @@
         <v>2022</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>54</v>
@@ -6952,7 +6961,7 @@
         <v>8</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>105.27</v>
+        <v>113.1</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>8</v>
@@ -6966,7 +6975,7 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>293</v>
@@ -6984,7 +6993,7 @@
         <v>8</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>105.27</v>
+        <v>112.93</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>8</v>
@@ -6995,10 +7004,10 @@
         <v>2022</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>295</v>
@@ -7016,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>105.11</v>
+        <v>111.94</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>8</v>
@@ -7030,7 +7039,7 @@
         <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -7048,7 +7057,7 @@
         <v>8</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>104.28</v>
+        <v>111.83</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>8</v>
@@ -7062,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7080,7 +7089,7 @@
         <v>8</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>104.19</v>
+        <v>111.8</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>8</v>
@@ -7094,7 +7103,7 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7112,7 +7121,7 @@
         <v>8</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>103.77</v>
+        <v>111.59</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>8</v>
@@ -7123,10 +7132,10 @@
         <v>2022</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7144,7 +7153,7 @@
         <v>8</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>103.6</v>
+        <v>110.91</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>8</v>
@@ -7155,10 +7164,10 @@
         <v>2022</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7176,7 +7185,7 @@
         <v>8</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>103.17</v>
+        <v>110.14</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>8</v>
@@ -7190,7 +7199,7 @@
         <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7208,7 +7217,7 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>102.6</v>
+        <v>110.01</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>8</v>
@@ -7222,7 +7231,7 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7240,7 +7249,7 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>102.43</v>
+        <v>109.77</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>8</v>
@@ -7251,10 +7260,10 @@
         <v>2022</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7272,7 +7281,7 @@
         <v>8</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>102.4</v>
+        <v>108.9</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>8</v>
@@ -7283,10 +7292,10 @@
         <v>2022</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7304,7 +7313,7 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>100.99</v>
+        <v>108.67</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>8</v>
@@ -7315,10 +7324,10 @@
         <v>2022</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7336,7 +7345,7 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>100.84</v>
+        <v>108.59</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>8</v>
@@ -7347,10 +7356,10 @@
         <v>2022</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7368,7 +7377,7 @@
         <v>8</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>100.75</v>
+        <v>108.41</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>8</v>
@@ -7382,7 +7391,7 @@
         <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7400,7 +7409,7 @@
         <v>8</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>100.63</v>
+        <v>108.04</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>8</v>
@@ -7414,7 +7423,7 @@
         <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7432,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>100.48</v>
+        <v>107.9</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>8</v>
@@ -7443,10 +7452,10 @@
         <v>2022</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7464,7 +7473,7 @@
         <v>8</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>100.19</v>
+        <v>107.4</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>8</v>
@@ -7475,10 +7484,10 @@
         <v>2022</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7496,7 +7505,7 @@
         <v>8</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>100.13</v>
+        <v>106.71</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>8</v>
@@ -7510,7 +7519,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7528,7 +7537,7 @@
         <v>8</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>98.78</v>
+        <v>106.06</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>8</v>
@@ -7542,7 +7551,7 @@
         <v>6</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7560,7 +7569,7 @@
         <v>8</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>96.58</v>
+        <v>103.95</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>8</v>
@@ -7571,7 +7580,7 @@
         <v>2022</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>54</v>
@@ -7592,7 +7601,7 @@
         <v>8</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>96.02</v>
+        <v>102.71</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>8</v>
@@ -7603,10 +7612,10 @@
         <v>2022</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7624,7 +7633,7 @@
         <v>8</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>95.94</v>
+        <v>102.66</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>8</v>
@@ -7635,10 +7644,10 @@
         <v>2022</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7656,7 +7665,7 @@
         <v>8</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>95.79</v>
+        <v>102.06</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>8</v>
@@ -7670,7 +7679,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7688,7 +7697,7 @@
         <v>8</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>95.68</v>
+        <v>101.45</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>8</v>
@@ -7702,7 +7711,7 @@
         <v>7</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7720,7 +7729,7 @@
         <v>8</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>93.72</v>
+        <v>100.01</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>8</v>
@@ -7734,7 +7743,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7752,7 +7761,7 @@
         <v>8</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>92.31</v>
+        <v>98.89</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>8</v>
@@ -7766,7 +7775,7 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7784,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>91.09</v>
+        <v>97.97</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>8</v>
@@ -7798,7 +7807,7 @@
         <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7816,7 +7825,7 @@
         <v>8</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>91.03</v>
+        <v>97.56</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>8</v>
@@ -7830,7 +7839,7 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7848,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>90.84</v>
+        <v>96.31</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>8</v>
@@ -7862,7 +7871,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7880,7 +7889,7 @@
         <v>8</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>89.04</v>
+        <v>95.85</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>8</v>
@@ -7894,7 +7903,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7912,7 +7921,7 @@
         <v>8</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>88.78</v>
+        <v>95.34</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>8</v>
@@ -7926,7 +7935,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7944,7 +7953,7 @@
         <v>8</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>88.67</v>
+        <v>95.13</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>8</v>
@@ -7958,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7976,7 +7985,7 @@
         <v>8</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>87.55</v>
+        <v>93.45</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>8</v>
@@ -7987,10 +7996,10 @@
         <v>2022</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -8008,7 +8017,7 @@
         <v>8</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>87.27</v>
+        <v>93.19</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>8</v>
@@ -8019,10 +8028,10 @@
         <v>2022</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -8040,7 +8049,7 @@
         <v>8</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>86.78</v>
+        <v>92.65</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>8</v>
@@ -8054,7 +8063,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8072,7 +8081,7 @@
         <v>8</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>86.01</v>
+        <v>92.02</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>8</v>
@@ -8086,7 +8095,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8104,7 +8113,7 @@
         <v>8</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>85.44</v>
+        <v>91.35</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>8</v>
@@ -8118,7 +8127,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8136,7 +8145,7 @@
         <v>8</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>84.35</v>
+        <v>90.41</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>8</v>
@@ -8150,7 +8159,7 @@
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8168,7 +8177,7 @@
         <v>8</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>83.54</v>
+        <v>90.09</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>8</v>
@@ -8182,7 +8191,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8200,7 +8209,7 @@
         <v>8</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>82.93</v>
+        <v>88.34</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>8</v>
@@ -8211,10 +8220,10 @@
         <v>2022</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8232,7 +8241,7 @@
         <v>8</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>81.89</v>
+        <v>87.52</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>8</v>
@@ -8243,10 +8252,10 @@
         <v>2022</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8264,7 +8273,7 @@
         <v>8</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>80.56</v>
+        <v>86.11</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>8</v>
@@ -8278,7 +8287,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8296,7 +8305,7 @@
         <v>8</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>79.81</v>
+        <v>85.51</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>8</v>
@@ -8310,7 +8319,7 @@
         <v>5</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8328,7 +8337,7 @@
         <v>8</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>79.63</v>
+        <v>85.19</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>8</v>
@@ -8342,7 +8351,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8360,7 +8369,7 @@
         <v>8</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>77.76</v>
+        <v>83.41</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>8</v>
@@ -8374,7 +8383,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8392,7 +8401,7 @@
         <v>8</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>75.61</v>
+        <v>81.58</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>8</v>
@@ -8424,7 +8433,7 @@
         <v>8</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>73.13</v>
+        <v>76.61</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>8</v>
@@ -8438,7 +8447,7 @@
         <v>6</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8456,7 +8465,7 @@
         <v>8</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>69.98</v>
+        <v>75.21</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>8</v>
@@ -8470,7 +8479,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>387</v>
@@ -8488,7 +8497,7 @@
         <v>8</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>67.77</v>
+        <v>72.21</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>8</v>
@@ -8502,7 +8511,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>389</v>
@@ -8520,7 +8529,7 @@
         <v>8</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>67.51</v>
+        <v>72.15</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>8</v>
@@ -8534,7 +8543,7 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>391</v>
@@ -8552,7 +8561,7 @@
         <v>8</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>62.04</v>
+        <v>66.6</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>8</v>
@@ -8566,7 +8575,7 @@
         <v>5</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>393</v>
@@ -8584,7 +8593,7 @@
         <v>8</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>59.73</v>
+        <v>61.58</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>8</v>
@@ -8598,13 +8607,13 @@
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>395</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>57</v>
@@ -8616,7 +8625,7 @@
         <v>8</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>53.39</v>
+        <v>57.11</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>8</v>
@@ -8630,7 +8639,7 @@
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>396</v>
@@ -8648,7 +8657,7 @@
         <v>8</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>50.04</v>
+        <v>52.19</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>8</v>
@@ -8662,7 +8671,7 @@
         <v>13</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>398</v>
@@ -8680,7 +8689,7 @@
         <v>8</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>47.32</v>
+        <v>50.63</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>8</v>
@@ -8694,7 +8703,7 @@
         <v>13</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>400</v>
@@ -8712,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>42.78</v>
+        <v>45.6</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>8</v>
@@ -8744,7 +8753,7 @@
         <v>8</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>187.84</v>
+        <v>207.43</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>8</v>
@@ -8776,7 +8785,7 @@
         <v>8</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>163.32</v>
+        <v>178.55</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>8</v>
@@ -8808,7 +8817,7 @@
         <v>8</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>162.62</v>
+        <v>174.81</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>8</v>
@@ -8840,7 +8849,7 @@
         <v>8</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>150.77</v>
+        <v>158.06</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>8</v>
@@ -8872,7 +8881,7 @@
         <v>8</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>129</v>
+        <v>138.56</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>8</v>
@@ -8904,7 +8913,7 @@
         <v>8</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>118.48</v>
+        <v>127.15</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>8</v>
@@ -8936,7 +8945,7 @@
         <v>8</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>115.93</v>
+        <v>124.45</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>8</v>
@@ -8968,7 +8977,7 @@
         <v>8</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>110.21</v>
+        <v>117.99</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>8</v>
@@ -9000,7 +9009,7 @@
         <v>8</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>110.09</v>
+        <v>117.87</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>8</v>
@@ -9032,7 +9041,7 @@
         <v>8</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>109.26</v>
+        <v>117.29</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>8</v>
@@ -9064,7 +9073,7 @@
         <v>8</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>107.4</v>
+        <v>115.37</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>8</v>
@@ -9096,7 +9105,7 @@
         <v>8</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>106.16</v>
+        <v>113.87</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>8</v>
@@ -9128,7 +9137,7 @@
         <v>8</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>106.03</v>
+        <v>113.47</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>8</v>
@@ -9160,7 +9169,7 @@
         <v>8</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>104.59</v>
+        <v>112.12</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>8</v>
@@ -9192,7 +9201,7 @@
         <v>8</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>99.6</v>
+        <v>106.89</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>8</v>
@@ -9224,7 +9233,7 @@
         <v>8</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>99.07</v>
+        <v>106.65</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>8</v>
@@ -9235,10 +9244,10 @@
         <v>2022</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>439</v>
@@ -9256,7 +9265,7 @@
         <v>8</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>97.78</v>
+        <v>103.43</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>8</v>
@@ -9267,10 +9276,10 @@
         <v>2022</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>441</v>
@@ -9288,7 +9297,7 @@
         <v>8</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>96.56</v>
+        <v>102.33</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>8</v>
@@ -9320,7 +9329,7 @@
         <v>8</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>94.47</v>
+        <v>101.86</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>8</v>
@@ -9352,7 +9361,7 @@
         <v>8</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>94.33</v>
+        <v>101.53</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>8</v>
@@ -9384,7 +9393,7 @@
         <v>8</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>94.24</v>
+        <v>101.26</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>8</v>
@@ -9416,7 +9425,7 @@
         <v>8</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>91.17</v>
+        <v>98.52</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>8</v>
@@ -9448,7 +9457,7 @@
         <v>8</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>89.56</v>
+        <v>95.79</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>8</v>
@@ -9480,7 +9489,7 @@
         <v>8</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>88.75</v>
+        <v>94.86</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>8</v>
@@ -9512,7 +9521,7 @@
         <v>8</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>86.61</v>
+        <v>93.01</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>8</v>
@@ -9523,10 +9532,10 @@
         <v>2022</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9544,7 +9553,7 @@
         <v>8</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>86.08</v>
+        <v>92.54</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>8</v>
@@ -9555,10 +9564,10 @@
         <v>2022</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9576,7 +9585,7 @@
         <v>8</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>85.85</v>
+        <v>91.7</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>8</v>
@@ -9587,10 +9596,10 @@
         <v>2022</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9608,7 +9617,7 @@
         <v>8</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>85.81</v>
+        <v>91.3</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>8</v>
@@ -9640,7 +9649,7 @@
         <v>8</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>84.76</v>
+        <v>90.31</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>8</v>
@@ -9672,7 +9681,7 @@
         <v>8</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>78.87</v>
+        <v>84.76</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>8</v>
@@ -9704,7 +9713,7 @@
         <v>8</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>76.62</v>
+        <v>80.82</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>8</v>
@@ -9736,7 +9745,7 @@
         <v>8</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>73.8</v>
+        <v>79.24</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>8</v>
@@ -9768,7 +9777,7 @@
         <v>8</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>73.47</v>
+        <v>79.1</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>8</v>
@@ -9800,7 +9809,7 @@
         <v>8</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>72.09</v>
+        <v>75.61</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>8</v>
@@ -9832,7 +9841,7 @@
         <v>8</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>68.53</v>
+        <v>73.32</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>8</v>
@@ -9864,7 +9873,7 @@
         <v>8</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>65.38</v>
+        <v>70.65</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>8</v>
@@ -9896,7 +9905,7 @@
         <v>8</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>63.21</v>
+        <v>67.37</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>8</v>
@@ -9928,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>62.18</v>
+        <v>66.08</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>8</v>
@@ -9960,7 +9969,7 @@
         <v>8</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>60.93</v>
+        <v>65.21</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>8</v>
@@ -9992,7 +10001,7 @@
         <v>8</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>58.46</v>
+        <v>62.32</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>8</v>
@@ -10024,7 +10033,7 @@
         <v>8</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>50.11</v>
+        <v>53.22</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>8</v>
@@ -10056,7 +10065,7 @@
         <v>8</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>39.09</v>
+        <v>42.31</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>8</v>
@@ -10088,7 +10097,7 @@
         <v>8</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>36.83</v>
+        <v>39.32</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>8</v>
@@ -10120,7 +10129,7 @@
         <v>8</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>165.44</v>
+        <v>178.89</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>8</v>
@@ -10152,7 +10161,7 @@
         <v>8</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>161.3</v>
+        <v>171.47</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>8</v>
@@ -10184,7 +10193,7 @@
         <v>8</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>157.14</v>
+        <v>170.33</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>8</v>
@@ -10195,10 +10204,10 @@
         <v>2022</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>503</v>
@@ -10216,7 +10225,7 @@
         <v>8</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>157.12</v>
+        <v>170.01</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>8</v>
@@ -10227,10 +10236,10 @@
         <v>2022</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>505</v>
@@ -10248,7 +10257,7 @@
         <v>8</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>155.79</v>
+        <v>168.7</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>8</v>
@@ -10280,7 +10289,7 @@
         <v>8</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>151.36</v>
+        <v>164.13</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>8</v>
@@ -10291,10 +10300,10 @@
         <v>2022</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>509</v>
@@ -10312,7 +10321,7 @@
         <v>8</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>150.85</v>
+        <v>162.17</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>8</v>
@@ -10323,10 +10332,10 @@
         <v>2022</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>511</v>
@@ -10344,7 +10353,7 @@
         <v>8</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>150.79</v>
+        <v>161.93</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>8</v>
@@ -10376,7 +10385,7 @@
         <v>8</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>145.28</v>
+        <v>156.47</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>8</v>
@@ -10408,7 +10417,7 @@
         <v>8</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>144.09</v>
+        <v>156.21</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>8</v>
@@ -10419,10 +10428,10 @@
         <v>2022</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>518</v>
@@ -10440,7 +10449,7 @@
         <v>8</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>142.94</v>
+        <v>155.79</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>8</v>
@@ -10451,10 +10460,10 @@
         <v>2022</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>520</v>
@@ -10472,7 +10481,7 @@
         <v>8</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>142.09</v>
+        <v>155.72</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>8</v>
@@ -10504,7 +10513,7 @@
         <v>8</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>141.39</v>
+        <v>154.88</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>8</v>
@@ -10536,7 +10545,7 @@
         <v>8</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>141.26</v>
+        <v>154.87</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>8</v>
@@ -10568,7 +10577,7 @@
         <v>8</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>138.48</v>
+        <v>149.47</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>8</v>
@@ -10600,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>138.34</v>
+        <v>149.35</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>8</v>
@@ -10611,10 +10620,10 @@
         <v>2022</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>530</v>
@@ -10632,7 +10641,7 @@
         <v>8</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>137.56</v>
+        <v>147.9</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>8</v>
@@ -10643,10 +10652,10 @@
         <v>2022</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>532</v>
@@ -10664,7 +10673,7 @@
         <v>8</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>137.32</v>
+        <v>147.19</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>8</v>
@@ -10696,7 +10705,7 @@
         <v>8</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>135.12</v>
+        <v>145.43</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>8</v>
@@ -10707,10 +10716,10 @@
         <v>2022</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>536</v>
@@ -10728,7 +10737,7 @@
         <v>8</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>134.99</v>
+        <v>145.21</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>8</v>
@@ -10739,10 +10748,10 @@
         <v>2022</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>538</v>
@@ -10760,7 +10769,7 @@
         <v>8</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>134.42</v>
+        <v>144.95</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>8</v>
@@ -10792,7 +10801,7 @@
         <v>8</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>133.99</v>
+        <v>144.13</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>8</v>
@@ -10824,7 +10833,7 @@
         <v>8</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>133.01</v>
+        <v>143.08</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>8</v>
@@ -10856,7 +10865,7 @@
         <v>8</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>132.07</v>
+        <v>141.73</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>8</v>
@@ -10867,10 +10876,10 @@
         <v>2022</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>546</v>
@@ -10888,7 +10897,7 @@
         <v>8</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>131.74</v>
+        <v>141.04</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>8</v>
@@ -10899,10 +10908,10 @@
         <v>2022</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>548</v>
@@ -10920,7 +10929,7 @@
         <v>8</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>128.86</v>
+        <v>140.99</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>8</v>
@@ -10952,7 +10961,7 @@
         <v>8</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>128.36</v>
+        <v>138.08</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>8</v>
@@ -10963,10 +10972,10 @@
         <v>2022</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>552</v>
@@ -10984,7 +10993,7 @@
         <v>8</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>127.51</v>
+        <v>137.6</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>8</v>
@@ -10995,10 +11004,10 @@
         <v>2022</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>554</v>
@@ -11016,7 +11025,7 @@
         <v>8</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>126.26</v>
+        <v>137.29</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>8</v>
@@ -11048,7 +11057,7 @@
         <v>8</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>126.21</v>
+        <v>137.17</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>8</v>
@@ -11059,10 +11068,10 @@
         <v>2022</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>558</v>
@@ -11080,7 +11089,7 @@
         <v>8</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>125.26</v>
+        <v>135.77</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>8</v>
@@ -11112,7 +11121,7 @@
         <v>8</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>125.26</v>
+        <v>135.64</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>8</v>
@@ -11123,10 +11132,10 @@
         <v>2022</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>562</v>
@@ -11144,7 +11153,7 @@
         <v>8</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>125.18</v>
+        <v>135.32</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>8</v>
@@ -11155,10 +11164,10 @@
         <v>2022</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>564</v>
@@ -11176,7 +11185,7 @@
         <v>8</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>124.62</v>
+        <v>135.17</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>8</v>
@@ -11208,7 +11217,7 @@
         <v>8</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>124.44</v>
+        <v>134.17</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>8</v>
@@ -11219,16 +11228,16 @@
         <v>2022</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C271" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D271" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D271" s="2" t="s">
+      <c r="E271" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>496</v>
@@ -11240,7 +11249,7 @@
         <v>8</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>123.28</v>
+        <v>134.1</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>8</v>
@@ -11251,10 +11260,10 @@
         <v>2022</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>493</v>
+        <v>570</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>571</v>
@@ -11272,7 +11281,7 @@
         <v>8</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>122.66</v>
+        <v>133.47</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>8</v>
@@ -11283,10 +11292,10 @@
         <v>2022</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>573</v>
@@ -11304,7 +11313,7 @@
         <v>8</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>122.13</v>
+        <v>131.58</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>8</v>
@@ -11315,10 +11324,10 @@
         <v>2022</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>575</v>
@@ -11336,7 +11345,7 @@
         <v>8</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>121.49</v>
+        <v>131.46</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>8</v>
@@ -11350,7 +11359,7 @@
         <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>577</v>
@@ -11368,7 +11377,7 @@
         <v>8</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>121.1</v>
+        <v>131.24</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>8</v>
@@ -11379,10 +11388,10 @@
         <v>2022</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>579</v>
@@ -11400,7 +11409,7 @@
         <v>8</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>121.06</v>
+        <v>129.77</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>8</v>
@@ -11411,10 +11420,10 @@
         <v>2022</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>581</v>
@@ -11432,7 +11441,7 @@
         <v>8</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>120.84</v>
+        <v>129.26</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>8</v>
@@ -11443,10 +11452,10 @@
         <v>2022</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>583</v>
@@ -11464,7 +11473,7 @@
         <v>8</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>120.11</v>
+        <v>128.81</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>8</v>
@@ -11475,10 +11484,10 @@
         <v>2022</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>585</v>
@@ -11496,7 +11505,7 @@
         <v>8</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>120.02</v>
+        <v>128.78</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>8</v>
@@ -11507,10 +11516,10 @@
         <v>2022</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>587</v>
@@ -11528,7 +11537,7 @@
         <v>8</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>119.65</v>
+        <v>128.43</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>8</v>
@@ -11542,7 +11551,7 @@
         <v>14</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>589</v>
@@ -11560,7 +11569,7 @@
         <v>8</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>118.78</v>
+        <v>127.97</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>8</v>
@@ -11592,7 +11601,7 @@
         <v>8</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>117.82</v>
+        <v>126.99</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>8</v>
@@ -11603,10 +11612,10 @@
         <v>2022</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>568</v>
+        <v>513</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>593</v>
@@ -11624,7 +11633,7 @@
         <v>8</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>117.57</v>
+        <v>126.87</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>8</v>
@@ -11635,10 +11644,10 @@
         <v>2022</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>513</v>
+        <v>570</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>595</v>
@@ -11656,7 +11665,7 @@
         <v>8</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>117.39</v>
+        <v>126.86</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>8</v>
@@ -11667,10 +11676,10 @@
         <v>2022</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>597</v>
@@ -11688,7 +11697,7 @@
         <v>8</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>117.07</v>
+        <v>126.54</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>8</v>
@@ -11699,10 +11708,10 @@
         <v>2022</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>599</v>
@@ -11720,7 +11729,7 @@
         <v>8</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>116.82</v>
+        <v>125.75</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>8</v>
@@ -11731,10 +11740,10 @@
         <v>2022</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>601</v>
@@ -11752,7 +11761,7 @@
         <v>8</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>115.51</v>
+        <v>125.18</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>8</v>
@@ -11763,10 +11772,10 @@
         <v>2022</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>603</v>
@@ -11784,7 +11793,7 @@
         <v>8</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>115.51</v>
+        <v>124.86</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>8</v>
@@ -11816,7 +11825,7 @@
         <v>8</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>114.76</v>
+        <v>123.95</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>8</v>
@@ -11848,7 +11857,7 @@
         <v>8</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>114.24</v>
+        <v>123.67</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>8</v>
@@ -11859,10 +11868,10 @@
         <v>2022</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>609</v>
@@ -11880,7 +11889,7 @@
         <v>8</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>113.4</v>
+        <v>123.64</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>8</v>
@@ -11891,10 +11900,10 @@
         <v>2022</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>568</v>
+        <v>513</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>611</v>
@@ -11912,7 +11921,7 @@
         <v>8</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>113.16</v>
+        <v>122.46</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>8</v>
@@ -11923,10 +11932,10 @@
         <v>2022</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>513</v>
+        <v>570</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>613</v>
@@ -11944,7 +11953,7 @@
         <v>8</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>113.14</v>
+        <v>121.67</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>8</v>
@@ -11958,7 +11967,7 @@
         <v>14</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>615</v>
@@ -11976,7 +11985,7 @@
         <v>8</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>112.27</v>
+        <v>121.61</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>8</v>
@@ -12008,7 +12017,7 @@
         <v>8</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>112.17</v>
+        <v>121.07</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>8</v>
@@ -12022,7 +12031,7 @@
         <v>14</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>619</v>
@@ -12040,7 +12049,7 @@
         <v>8</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>111.61</v>
+        <v>119.82</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>8</v>
@@ -12072,7 +12081,7 @@
         <v>8</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>108.91</v>
+        <v>117.41</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>8</v>
@@ -12104,7 +12113,7 @@
         <v>8</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>108.25</v>
+        <v>116.93</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>8</v>
@@ -12115,10 +12124,10 @@
         <v>2022</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>625</v>
@@ -12136,7 +12145,7 @@
         <v>8</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>107.87</v>
+        <v>116.46</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>8</v>
@@ -12147,16 +12156,16 @@
         <v>2022</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>568</v>
+        <v>513</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>627</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>493</v>
+        <v>628</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>496</v>
@@ -12168,7 +12177,7 @@
         <v>8</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>107.56</v>
+        <v>116.38</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>8</v>
@@ -12179,16 +12188,16 @@
         <v>2022</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>500</v>
+        <v>570</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>629</v>
+        <v>493</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>496</v>
@@ -12200,7 +12209,7 @@
         <v>8</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>107.42</v>
+        <v>116.03</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>8</v>
@@ -12211,10 +12220,10 @@
         <v>2022</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>630</v>
@@ -12232,7 +12241,7 @@
         <v>8</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>106.97</v>
+        <v>115.39</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>8</v>
@@ -12243,10 +12252,10 @@
         <v>2022</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>632</v>
@@ -12264,7 +12273,7 @@
         <v>8</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>106.71</v>
+        <v>115.19</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>8</v>
@@ -12296,7 +12305,7 @@
         <v>8</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>106.44</v>
+        <v>114.97</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>8</v>
@@ -12328,7 +12337,7 @@
         <v>8</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>106.26</v>
+        <v>114.07</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>8</v>
@@ -12360,7 +12369,7 @@
         <v>8</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>105.81</v>
+        <v>114.02</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>8</v>
@@ -12392,7 +12401,7 @@
         <v>8</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>104.51</v>
+        <v>113.08</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>8</v>
@@ -12424,7 +12433,7 @@
         <v>8</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>103.7</v>
+        <v>111.5</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>8</v>
@@ -12438,7 +12447,7 @@
         <v>14</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>644</v>
@@ -12456,7 +12465,7 @@
         <v>8</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>103.12</v>
+        <v>110.89</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>8</v>
@@ -12488,7 +12497,7 @@
         <v>8</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>100.17</v>
+        <v>107.88</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>8</v>
@@ -12520,7 +12529,7 @@
         <v>8</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>99.96</v>
+        <v>107.64</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>8</v>
@@ -12552,7 +12561,7 @@
         <v>8</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>99.84</v>
+        <v>107.22</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>8</v>
@@ -12584,7 +12593,7 @@
         <v>8</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>98.39</v>
+        <v>106.38</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>8</v>
@@ -12616,7 +12625,7 @@
         <v>8</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>97.93</v>
+        <v>105.48</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>8</v>
@@ -12648,7 +12657,7 @@
         <v>8</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>95.53</v>
+        <v>102.32</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>8</v>
@@ -12680,7 +12689,7 @@
         <v>8</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>95.35</v>
+        <v>102.3</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>8</v>
@@ -12712,7 +12721,7 @@
         <v>8</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>94.66</v>
+        <v>101.8</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>8</v>
@@ -12723,10 +12732,10 @@
         <v>2022</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>513</v>
+        <v>570</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>662</v>
@@ -12744,7 +12753,7 @@
         <v>8</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>94.39</v>
+        <v>101.15</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>8</v>
@@ -12755,10 +12764,10 @@
         <v>2022</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>568</v>
+        <v>513</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>664</v>
@@ -12776,7 +12785,7 @@
         <v>8</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>94.3</v>
+        <v>100.98</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>8</v>
@@ -12787,10 +12796,10 @@
         <v>2022</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>666</v>
@@ -12808,7 +12817,7 @@
         <v>8</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>94.13</v>
+        <v>100.22</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>8</v>
@@ -12840,7 +12849,7 @@
         <v>8</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>93.37</v>
+        <v>100.16</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>8</v>
@@ -12851,10 +12860,10 @@
         <v>2022</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>670</v>
@@ -12872,7 +12881,7 @@
         <v>8</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>92.4</v>
+        <v>99.92</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>8</v>
@@ -12904,7 +12913,7 @@
         <v>8</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>91.86</v>
+        <v>98.43</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>8</v>
@@ -12936,7 +12945,7 @@
         <v>8</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>91.54</v>
+        <v>98.41</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>8</v>
@@ -12968,7 +12977,7 @@
         <v>8</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>91.13</v>
+        <v>98.3</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>8</v>
@@ -13000,7 +13009,7 @@
         <v>8</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>90.36</v>
+        <v>96.71</v>
       </c>
       <c r="J326" s="2" t="s">
         <v>8</v>
@@ -13032,7 +13041,7 @@
         <v>8</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>89.83</v>
+        <v>96.06</v>
       </c>
       <c r="J327" s="2" t="s">
         <v>8</v>
@@ -13043,10 +13052,10 @@
         <v>2022</v>
       </c>
       <c r="B328" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>682</v>
@@ -13064,7 +13073,7 @@
         <v>8</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>88.21</v>
+        <v>95.44</v>
       </c>
       <c r="J328" s="2" t="s">
         <v>8</v>
@@ -13075,10 +13084,10 @@
         <v>2022</v>
       </c>
       <c r="B329" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>684</v>
@@ -13096,7 +13105,7 @@
         <v>8</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>88.02</v>
+        <v>94.8</v>
       </c>
       <c r="J329" s="2" t="s">
         <v>8</v>
@@ -13107,10 +13116,10 @@
         <v>2022</v>
       </c>
       <c r="B330" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>500</v>
+        <v>570</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>686</v>
@@ -13128,7 +13137,7 @@
         <v>8</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>87.72</v>
+        <v>94.8</v>
       </c>
       <c r="J330" s="2" t="s">
         <v>8</v>
@@ -13139,10 +13148,10 @@
         <v>2022</v>
       </c>
       <c r="B331" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>568</v>
+        <v>500</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>688</v>
@@ -13160,7 +13169,7 @@
         <v>8</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>87.68</v>
+        <v>94.26</v>
       </c>
       <c r="J331" s="2" t="s">
         <v>8</v>
@@ -13192,7 +13201,7 @@
         <v>8</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>86.42</v>
+        <v>92.71</v>
       </c>
       <c r="J332" s="2" t="s">
         <v>8</v>
@@ -13203,10 +13212,10 @@
         <v>2022</v>
       </c>
       <c r="B333" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>692</v>
@@ -13224,7 +13233,7 @@
         <v>8</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>82.54</v>
+        <v>88.12</v>
       </c>
       <c r="J333" s="2" t="s">
         <v>8</v>
@@ -13235,10 +13244,10 @@
         <v>2022</v>
       </c>
       <c r="B334" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>694</v>
@@ -13256,7 +13265,7 @@
         <v>8</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>82.22</v>
+        <v>87.98</v>
       </c>
       <c r="J334" s="2" t="s">
         <v>8</v>
@@ -13288,7 +13297,7 @@
         <v>8</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>79.73</v>
+        <v>86.2</v>
       </c>
       <c r="J335" s="2" t="s">
         <v>8</v>
@@ -13320,7 +13329,7 @@
         <v>8</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>76.61</v>
+        <v>81.99</v>
       </c>
       <c r="J336" s="2" t="s">
         <v>8</v>
@@ -13352,7 +13361,7 @@
         <v>8</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>74.35</v>
+        <v>80.06</v>
       </c>
       <c r="J337" s="2" t="s">
         <v>8</v>
@@ -13384,7 +13393,7 @@
         <v>8</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>73.97</v>
+        <v>79.71</v>
       </c>
       <c r="J338" s="2" t="s">
         <v>8</v>
@@ -13416,7 +13425,7 @@
         <v>8</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>69.29</v>
+        <v>74.23</v>
       </c>
       <c r="J339" s="2" t="s">
         <v>8</v>
@@ -13448,7 +13457,7 @@
         <v>8</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>64.96</v>
+        <v>69.63</v>
       </c>
       <c r="J340" s="2" t="s">
         <v>8</v>
@@ -13462,7 +13471,7 @@
         <v>14</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>708</v>
@@ -13480,7 +13489,7 @@
         <v>8</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>58.78</v>
+        <v>62.21</v>
       </c>
       <c r="J341" s="2" t="s">
         <v>8</v>
@@ -13512,7 +13521,7 @@
         <v>8</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>50.67</v>
+        <v>54.11</v>
       </c>
       <c r="J342" s="2" t="s">
         <v>8</v>
@@ -13571,23 +13580,23 @@
         <v>719</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -13609,21 +13618,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
@@ -13632,7 +13641,7 @@
         <v>2022</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:42</t>
+    <t xml:space="preserve">2026-09-07 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2022.xlsx
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:41</t>
+    <t xml:space="preserve">2026-09-08 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
